--- a/api/public/templates/modeleImportMembreUpdate.xlsx
+++ b/api/public/templates/modeleImportMembreUpdate.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User2\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User2\Desktop\Bureau\Code_source_dev\Gestion_oecfm\api\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB22B15-B6FE-44F1-B444-2FF35DF2CAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA74C94F-5800-4B8B-8B90-0D8AA35BABFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6F3DCEDA-1085-40B5-B960-A0064D832EBD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6F3DCEDA-1085-40B5-B960-A0064D832EBD}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>date_modification</t>
+  </si>
+  <si>
+    <t>membre_id</t>
+  </si>
+  <si>
+    <t>membre_active</t>
+  </si>
   <si>
     <t>situation</t>
   </si>
@@ -45,15 +54,6 @@
     <t>adresse</t>
   </si>
   <si>
-    <t>date_modification</t>
-  </si>
-  <si>
-    <t>membre_id</t>
-  </si>
-  <si>
-    <t>membre_active</t>
-  </si>
-  <si>
     <t>ville</t>
   </si>
   <si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>nombre_associe</t>
+  </si>
+  <si>
+    <t>diplôme</t>
   </si>
 </sst>
 </file>
@@ -454,105 +457,107 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7D4EC85-EFB0-4814-8BB7-4875AADF8F77}">
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" customWidth="1"/>
     <col min="3" max="3" width="14.5546875" customWidth="1"/>
-    <col min="20" max="20" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+      <c r="H1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D12" s="2"/>
+    <row r="3" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C12" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
